--- a/Tubing size lenght and Bought out part list_400.xlsx
+++ b/Tubing size lenght and Bought out part list_400.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/782417d650b27398/Desktop/Sharad Akshay/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C1DEB2-B220-4961-AEAC-7BA1E8D9479E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{82C1DEB2-B220-4961-AEAC-7BA1E8D9479E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B16F535A-94E5-4650-861E-ABA986D68AA1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="354" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="354" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tube lenght400" sheetId="4" r:id="rId1"/>
@@ -1268,6 +1268,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1276,9 +1279,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1604,34 +1604,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C5A2DA-0904-46AA-85D8-95F270399086}">
   <dimension ref="B2:I14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E2" s="4">
         <v>46113</v>
       </c>
       <c r="G2" s="14"/>
     </row>
-    <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="70" t="s">
+    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
-    </row>
-    <row r="4" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="73"/>
+    </row>
+    <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="7">
         <v>1</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="2:9" s="64" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" s="64" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="59">
         <v>2</v>
       </c>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="H7" s="61"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <v>2</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="7">
         <v>3</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="7">
         <v>4</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="7">
         <v>5</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="7">
         <v>7</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="7">
         <v>8</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>9</v>
       </c>
@@ -1871,32 +1871,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B894E20D-C11B-4422-A0CB-B6C9E489795F}">
   <dimension ref="A2:I94"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="60.7109375" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="60.6640625" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="5" max="5" width="20.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E2" s="4">
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C4" s="18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:8" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:8" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="17" t="s">
         <v>27</v>
       </c>
@@ -1913,8 +1913,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="73" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="70" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="25">
@@ -1939,8 +1939,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="73"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="70"/>
       <c r="B9" s="25">
         <v>2</v>
       </c>
@@ -1963,8 +1963,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="73"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="70"/>
       <c r="B10" s="25">
         <v>3</v>
       </c>
@@ -1984,8 +1984,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="73"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="70"/>
       <c r="B11" s="25">
         <v>4</v>
       </c>
@@ -2008,8 +2008,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="73"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="70"/>
       <c r="B12" s="25">
         <v>5</v>
       </c>
@@ -2029,8 +2029,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="70"/>
       <c r="B13" s="25">
         <v>6</v>
       </c>
@@ -2053,8 +2053,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="73"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="70"/>
       <c r="B14" s="25">
         <v>7</v>
       </c>
@@ -2077,8 +2077,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="73"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="70"/>
       <c r="B15" s="25">
         <v>8</v>
       </c>
@@ -2098,8 +2098,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="73"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="70"/>
       <c r="B16" s="25">
         <v>9</v>
       </c>
@@ -2119,8 +2119,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="73"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
       <c r="B17" s="25">
         <v>10</v>
       </c>
@@ -2140,8 +2140,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="73"/>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="70"/>
       <c r="B18" s="25">
         <v>11</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B19" s="25">
         <v>12</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B20" s="25">
         <v>13</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B21" s="25">
         <v>14</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B22" s="25">
         <v>15</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B23" s="25">
         <v>16</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B24" s="25">
         <v>17</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B25" s="25">
         <v>18</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B26" s="25">
         <v>19</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B27" s="25">
         <v>20</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B28" s="25">
         <v>21</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B29" s="25">
         <v>22</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B30" s="25">
         <v>23</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B31" s="25">
         <v>24</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B32" s="25">
         <v>25</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="25">
         <v>26</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="25">
         <v>27</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="25">
         <v>28</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="25">
         <v>29</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="25">
         <v>30</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="25">
         <v>31</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="25">
         <v>32</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="25">
         <v>33</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="25">
         <v>34</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="25">
         <v>35</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="25">
         <v>36</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="25">
         <v>37</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="25">
         <v>38</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="25">
         <v>39</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="25">
         <v>40</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="25">
         <v>41</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49" s="25">
         <v>42</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50" s="25">
         <v>43</v>
       </c>
@@ -2840,7 +2840,7 @@
       <c r="E50" s="29"/>
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51" s="25">
         <v>44</v>
       </c>
@@ -2851,7 +2851,7 @@
       <c r="E51" s="29"/>
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52" s="25">
         <v>45</v>
       </c>
@@ -2862,7 +2862,7 @@
       <c r="E52" s="29"/>
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53" s="25">
         <v>46</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54" s="25">
         <v>47</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55" s="25">
         <v>48</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="25">
         <v>49</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57" s="25">
         <v>50</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="25">
         <v>51</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59" s="25">
         <v>52</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60" s="25">
         <v>53</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="25">
         <v>54</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="25">
         <v>55</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="25">
         <v>56</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="25">
         <v>57</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="25">
         <v>58</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="25">
         <v>59</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="25">
         <v>60</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B68" s="25">
         <v>61</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="25">
         <v>62</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="25">
         <v>63</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="25">
         <v>64</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B72" s="25">
         <v>65</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="25">
         <v>66</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="25">
         <v>67</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="25">
         <v>68</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="25">
         <v>69</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="25">
         <v>70</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="25">
         <v>71</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="25">
         <v>72</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="25">
         <v>73</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="25">
         <v>74</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="25">
         <v>75</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="25">
         <v>76</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B84" s="46">
         <v>77</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="25">
         <v>78</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="25">
         <v>79</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="25">
         <v>80</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="25">
         <v>81</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="25">
         <v>82</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="1"/>
       <c r="C90" s="32" t="s">
         <v>127</v>
@@ -3657,28 +3657,28 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="1"/>
       <c r="C91" s="32"/>
       <c r="D91" s="35"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="1"/>
       <c r="C92" s="32"/>
       <c r="D92" s="35"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="1"/>
       <c r="C93" s="30"/>
       <c r="D93" s="35"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="1"/>
       <c r="C94" s="30"/>
       <c r="D94" s="35"/>
@@ -3696,10 +3696,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{085ACBFE-4DAC-40D4-8992-361318713CD5}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="2"/>
-    <col min="4" max="5" width="8.85546875" style="2"/>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="4" max="5" width="8.88671875" style="2"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
